--- a/Data/portfolio_by_Asset_class_2026_06_10.xlsx
+++ b/Data/portfolio_by_Asset_class_2026_06_10.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bfraenkel/Documents/Code/Financial_Plan/Data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E429F13C-AE62-3B40-AD35-C844C72ECC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="20180" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Asset_class</t>
   </si>
@@ -22,13 +41,16 @@
     <t>Market Value</t>
   </si>
   <si>
-    <t>Emerging Mkts Stks</t>
-  </si>
-  <si>
-    <t>Foreign Industrialzed Mkts Stocks</t>
-  </si>
-  <si>
-    <t>Non-U.S. Bonds</t>
+    <t>Non-US Dev Bonds</t>
+  </si>
+  <si>
+    <t>Non-US Dev Stk</t>
+  </si>
+  <si>
+    <t>Non-US Emrg Bonds</t>
+  </si>
+  <si>
+    <t>Non-US Emrg Stk</t>
   </si>
   <si>
     <t>U.S. High Yield Bonds</t>
@@ -37,9 +59,6 @@
     <t>U.S. Investment Grade Bonds</t>
   </si>
   <si>
-    <t>U.S. Lg Cap Growth</t>
-  </si>
-  <si>
     <t>U.S. Lg Cap Val</t>
   </si>
   <si>
@@ -50,13 +69,43 @@
   </si>
   <si>
     <t>U.S. Sm Cap Val</t>
+  </si>
+  <si>
+    <t>US High Yield Bonds</t>
+  </si>
+  <si>
+    <t>US Infl Protected Bonds</t>
+  </si>
+  <si>
+    <t>US Large Cap Growth</t>
+  </si>
+  <si>
+    <t>US Large Cap Value</t>
+  </si>
+  <si>
+    <t>US Mid Cap Growth</t>
+  </si>
+  <si>
+    <t>US Small Cap Growth</t>
+  </si>
+  <si>
+    <t>US Small Cap Value</t>
+  </si>
+  <si>
+    <t>US Txbl Int Term Bonds</t>
+  </si>
+  <si>
+    <t>US Txbl Long Term Bonds</t>
+  </si>
+  <si>
+    <t>US Txbl Short Term Bonds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,13 +168,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -163,7 +220,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -197,6 +254,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -231,9 +289,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -406,11 +465,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -418,84 +480,164 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>265572.37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>95953.389999999985</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
-        <v>897047.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>920489.65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>73895.64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>15162.09</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>134857.22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>265572.37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>602435.09</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>120038.39999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>618659.88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>24460.52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
-        <v>505416.14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>75518.26999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
-        <v>263366.63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>24923.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
-        <v>247851.48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>102197.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11">
-        <v>88326.98000000001</v>
+        <v>63452.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>14818.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>129068.78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>618659.88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>406455.72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>238442.88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>145654.07999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>24874.58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>147335.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>125504.97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>138845.48000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Data/portfolio_by_Asset_class_2026_06_10.xlsx
+++ b/Data/portfolio_by_Asset_class_2026_06_10.xlsx
@@ -1,39 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bfraenkel/Documents/Code/Financial_Plan/Data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E429F13C-AE62-3B40-AD35-C844C72ECC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="20180" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Asset_class</t>
   </si>
@@ -41,16 +22,13 @@
     <t>Market Value</t>
   </si>
   <si>
-    <t>Non-US Dev Bonds</t>
-  </si>
-  <si>
-    <t>Non-US Dev Stk</t>
-  </si>
-  <si>
-    <t>Non-US Emrg Bonds</t>
-  </si>
-  <si>
-    <t>Non-US Emrg Stk</t>
+    <t>Emerging Mkts Stks</t>
+  </si>
+  <si>
+    <t>Foreign Industrialzed Mkts Stocks</t>
+  </si>
+  <si>
+    <t>Non-U.S. Bonds</t>
   </si>
   <si>
     <t>U.S. High Yield Bonds</t>
@@ -59,6 +37,9 @@
     <t>U.S. Investment Grade Bonds</t>
   </si>
   <si>
+    <t>U.S. Lg Cap Growth</t>
+  </si>
+  <si>
     <t>U.S. Lg Cap Val</t>
   </si>
   <si>
@@ -69,43 +50,13 @@
   </si>
   <si>
     <t>U.S. Sm Cap Val</t>
-  </si>
-  <si>
-    <t>US High Yield Bonds</t>
-  </si>
-  <si>
-    <t>US Infl Protected Bonds</t>
-  </si>
-  <si>
-    <t>US Large Cap Growth</t>
-  </si>
-  <si>
-    <t>US Large Cap Value</t>
-  </si>
-  <si>
-    <t>US Mid Cap Growth</t>
-  </si>
-  <si>
-    <t>US Small Cap Growth</t>
-  </si>
-  <si>
-    <t>US Small Cap Value</t>
-  </si>
-  <si>
-    <t>US Txbl Int Term Bonds</t>
-  </si>
-  <si>
-    <t>US Txbl Long Term Bonds</t>
-  </si>
-  <si>
-    <t>US Txbl Short Term Bonds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,21 +119,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -220,7 +163,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -254,7 +197,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -289,10 +231,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -465,14 +406,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,164 +418,84 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>95953.389999999985</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>265572.37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
-        <v>920489.65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>897047.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>15162.09</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>73895.64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>265572.37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>134857.22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>120038.39999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>602435.09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>24460.52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>618659.88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
-        <v>75518.26999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>505416.14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
-        <v>24923.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>263366.63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
-        <v>102197.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>247851.48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11">
-        <v>63452.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>14818.82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>129068.78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>618659.88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>406455.72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>238442.88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>145654.07999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
-        <v>24874.58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
-        <v>147335.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
-        <v>125504.97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
-        <v>138845.48000000001</v>
+        <v>88326.98000000001</v>
       </c>
     </row>
   </sheetData>
